--- a/artfynd/A 29539-2025 artfynd.xlsx
+++ b/artfynd/A 29539-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132614880</v>
       </c>
       <c r="B2" t="n">
-        <v>91918</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,48 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132614879</v>
+        <v>133030112</v>
       </c>
       <c r="B3" t="n">
-        <v>79952</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tannsjön S, Jmt</t>
+          <t>Flintflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532728</v>
+        <v>532656</v>
       </c>
       <c r="R3" t="n">
-        <v>7042015</v>
+        <v>7042057</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -840,9 +840,19 @@
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,14 +879,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133030116</v>
+        <v>133030113</v>
       </c>
       <c r="B4" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -904,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532555</v>
+        <v>532562</v>
       </c>
       <c r="R4" t="n">
-        <v>7042169</v>
+        <v>7042053</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -939,7 +949,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -949,7 +959,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133030095</v>
+        <v>133030115</v>
       </c>
       <c r="B5" t="n">
-        <v>79924</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532716</v>
+        <v>532565</v>
       </c>
       <c r="R5" t="n">
-        <v>7042033</v>
+        <v>7042104</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1046,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1056,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,14 +1093,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133030115</v>
+        <v>133030116</v>
       </c>
       <c r="B6" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1118,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532565</v>
+        <v>532555</v>
       </c>
       <c r="R6" t="n">
-        <v>7042104</v>
+        <v>7042169</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1153,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1163,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,11 +1203,11 @@
         <v>133030117</v>
       </c>
       <c r="B7" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1297,32 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133030120</v>
+        <v>133030118</v>
       </c>
       <c r="B8" t="n">
-        <v>78737</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532713</v>
+        <v>532480</v>
       </c>
       <c r="R8" t="n">
-        <v>7042027</v>
+        <v>7042169</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1367,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1377,7 +1387,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133030113</v>
+        <v>133030120</v>
       </c>
       <c r="B9" t="n">
-        <v>79334</v>
+        <v>78776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532562</v>
+        <v>532713</v>
       </c>
       <c r="R9" t="n">
-        <v>7042053</v>
+        <v>7042027</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1474,7 +1484,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1484,7 +1494,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133030112</v>
+        <v>133030090</v>
       </c>
       <c r="B10" t="n">
-        <v>79334</v>
+        <v>83358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532656</v>
+        <v>532632</v>
       </c>
       <c r="R10" t="n">
-        <v>7042057</v>
+        <v>7042039</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1581,7 +1591,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1591,7 +1601,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133030090</v>
+        <v>133030091</v>
       </c>
       <c r="B11" t="n">
-        <v>83319</v>
+        <v>83358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532632</v>
+        <v>532556</v>
       </c>
       <c r="R11" t="n">
-        <v>7042039</v>
+        <v>7042171</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1688,7 +1698,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1698,7 +1708,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133030094</v>
+        <v>132614879</v>
       </c>
       <c r="B12" t="n">
-        <v>79953</v>
+        <v>79992</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,17 +1766,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Flintflotjärnen, Jmt</t>
+          <t>Tannsjön S, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532425</v>
+        <v>532728</v>
       </c>
       <c r="R12" t="n">
-        <v>7042166</v>
+        <v>7042015</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1793,19 +1803,9 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:12</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133030118</v>
+        <v>133030092</v>
       </c>
       <c r="B13" t="n">
-        <v>79334</v>
+        <v>79992</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532480</v>
+        <v>532720</v>
       </c>
       <c r="R13" t="n">
-        <v>7042169</v>
+        <v>7042036</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133030099</v>
+        <v>133030093</v>
       </c>
       <c r="B14" t="n">
-        <v>57955</v>
+        <v>79992</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1950,39 +1950,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flintflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532551</v>
+        <v>532582</v>
       </c>
       <c r="R14" t="n">
-        <v>7042162</v>
+        <v>7042030</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2014,7 +2009,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2024,7 +2019,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133030091</v>
+        <v>133030094</v>
       </c>
       <c r="B15" t="n">
-        <v>83319</v>
+        <v>79992</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,21 +2057,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532556</v>
+        <v>532425</v>
       </c>
       <c r="R15" t="n">
-        <v>7042171</v>
+        <v>7042166</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2121,7 +2116,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2131,7 +2126,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,45 +2153,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133030093</v>
+        <v>133030099</v>
       </c>
       <c r="B16" t="n">
-        <v>79953</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flintflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>532582</v>
+        <v>532551</v>
       </c>
       <c r="R16" t="n">
-        <v>7042030</v>
+        <v>7042162</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2268,11 +2268,11 @@
         <v>133030100</v>
       </c>
       <c r="B17" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2377,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133030092</v>
+        <v>132614882</v>
       </c>
       <c r="B18" t="n">
-        <v>79953</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2388,37 +2388,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Flintflotjärnen, Jmt</t>
+          <t>Tannsjön S, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532720</v>
+        <v>532749</v>
       </c>
       <c r="R18" t="n">
-        <v>7042036</v>
+        <v>7042032</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2445,19 +2445,14 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:01</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,7 +2479,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132614886</v>
+        <v>132614883</v>
       </c>
       <c r="B19" t="n">
         <v>57975</v>
@@ -2519,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532497</v>
+        <v>532595</v>
       </c>
       <c r="R19" t="n">
-        <v>7042056</v>
+        <v>7041994</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,7 +2554,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,7 +2581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132614893</v>
+        <v>132614884</v>
       </c>
       <c r="B20" t="n">
         <v>57975</v>
@@ -2621,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532445</v>
+        <v>532511</v>
       </c>
       <c r="R20" t="n">
-        <v>7042139</v>
+        <v>7042018</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,7 +2656,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,7 +2683,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133030096</v>
+        <v>132614886</v>
       </c>
       <c r="B21" t="n">
         <v>57975</v>
@@ -2716,40 +2711,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Flintflotjärnen, Jmt</t>
+          <t>Tannsjön S, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>532676</v>
+        <v>532497</v>
       </c>
       <c r="R21" t="n">
-        <v>7042178</v>
+        <v>7042056</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2776,19 +2751,14 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:21</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2785,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132614883</v>
+        <v>132614887</v>
       </c>
       <c r="B22" t="n">
         <v>57975</v>
@@ -2850,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>532595</v>
+        <v>532422</v>
       </c>
       <c r="R22" t="n">
-        <v>7041994</v>
+        <v>7042158</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2860,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2917,7 +2887,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132614884</v>
+        <v>132614888</v>
       </c>
       <c r="B23" t="n">
         <v>57975</v>
@@ -2952,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>532511</v>
+        <v>532427</v>
       </c>
       <c r="R23" t="n">
-        <v>7042018</v>
+        <v>7042157</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,7 +2989,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132614892</v>
+        <v>132614891</v>
       </c>
       <c r="B24" t="n">
         <v>57975</v>
@@ -3054,10 +3024,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>532441</v>
+        <v>532432</v>
       </c>
       <c r="R24" t="n">
-        <v>7042156</v>
+        <v>7042152</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,7 +3091,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132614891</v>
+        <v>132614892</v>
       </c>
       <c r="B25" t="n">
         <v>57975</v>
@@ -3156,10 +3126,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532432</v>
+        <v>532441</v>
       </c>
       <c r="R25" t="n">
-        <v>7042152</v>
+        <v>7042156</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3223,7 +3193,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132614882</v>
+        <v>132614893</v>
       </c>
       <c r="B26" t="n">
         <v>57975</v>
@@ -3258,10 +3228,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>532749</v>
+        <v>532445</v>
       </c>
       <c r="R26" t="n">
-        <v>7042032</v>
+        <v>7042139</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,7 +3268,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3325,7 +3295,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132614887</v>
+        <v>132614894</v>
       </c>
       <c r="B27" t="n">
         <v>57975</v>
@@ -3360,10 +3330,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>532422</v>
+        <v>532436</v>
       </c>
       <c r="R27" t="n">
-        <v>7042158</v>
+        <v>7042142</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3400,7 +3370,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,7 +3397,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132614894</v>
+        <v>133030096</v>
       </c>
       <c r="B28" t="n">
         <v>57975</v>
@@ -3455,20 +3425,40 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tannsjön S, Jmt</t>
+          <t>Flintflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>532436</v>
+        <v>532676</v>
       </c>
       <c r="R28" t="n">
-        <v>7042142</v>
+        <v>7042178</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3495,14 +3485,19 @@
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3529,10 +3524,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132614888</v>
+        <v>133030095</v>
       </c>
       <c r="B29" t="n">
-        <v>57975</v>
+        <v>79963</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3540,37 +3535,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tannsjön S, Jmt</t>
+          <t>Flintflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>532427</v>
+        <v>532716</v>
       </c>
       <c r="R29" t="n">
-        <v>7042157</v>
+        <v>7042033</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3597,14 +3592,19 @@
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 29539-2025 artfynd.xlsx
+++ b/artfynd/A 29539-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614880</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030112</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030113</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030115</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030116</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030117</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030118</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030120</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030090</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030091</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,6 +1884,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614879</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1936,6 +1996,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030092</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2043,6 +2108,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030093</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2150,6 +2220,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030094</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2262,6 +2337,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030099</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2374,6 +2454,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030100</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2476,6 +2561,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614882</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2578,6 +2668,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614883</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2680,6 +2775,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614884</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2782,6 +2882,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614886</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2884,6 +2989,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614887</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2986,6 +3096,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614888</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3088,6 +3203,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614891</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3190,6 +3310,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614892</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3292,6 +3417,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614893</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3394,6 +3524,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614894</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3521,6 +3656,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030096</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3628,8 +3768,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030095</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>